--- a/research/traditional_assets/database/data/france/france_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/france/france_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.127</v>
+        <v>0.0271</v>
       </c>
       <c r="E2">
-        <v>0.211</v>
+        <v>0.0003000000000000017</v>
       </c>
       <c r="F2">
-        <v>0.2435</v>
+        <v>0.00746</v>
       </c>
       <c r="G2">
-        <v>0.2540171322336978</v>
+        <v>0.3352567577515878</v>
       </c>
       <c r="H2">
-        <v>0.2540171322336978</v>
+        <v>0.3352567577515878</v>
       </c>
       <c r="I2">
-        <v>0.3469830550248988</v>
+        <v>0.3091632279949812</v>
       </c>
       <c r="J2">
-        <v>0.3162086539121178</v>
+        <v>0.2885104865689745</v>
       </c>
       <c r="K2">
-        <v>2321.092</v>
+        <v>1796.557</v>
       </c>
       <c r="L2">
-        <v>0.3027537235862411</v>
+        <v>0.2404691442300614</v>
       </c>
       <c r="M2">
-        <v>268.1851</v>
+        <v>392.952</v>
       </c>
       <c r="N2">
-        <v>0.008831316759260141</v>
+        <v>0.01775775731444605</v>
       </c>
       <c r="O2">
-        <v>0.1155426411361549</v>
+        <v>0.2187250390608258</v>
       </c>
       <c r="P2">
-        <v>257.1941</v>
+        <v>391.901</v>
       </c>
       <c r="Q2">
-        <v>0.008469383890875478</v>
+        <v>0.01771026193857958</v>
       </c>
       <c r="R2">
-        <v>0.1108073699793028</v>
+        <v>0.2181400311818662</v>
       </c>
       <c r="S2">
-        <v>10.991</v>
+        <v>1.050999999999998</v>
       </c>
       <c r="T2">
-        <v>0.04098288831109558</v>
+        <v>0.002674626926443937</v>
       </c>
       <c r="U2">
-        <v>1472.519</v>
+        <v>1210.165</v>
       </c>
       <c r="V2">
-        <v>0.04848994863260109</v>
+        <v>0.05468814608511117</v>
       </c>
       <c r="W2">
-        <v>0.06672210840769974</v>
+        <v>0.09296124515781611</v>
       </c>
       <c r="X2">
-        <v>0.04846516549922482</v>
+        <v>0.0786283283438169</v>
       </c>
       <c r="Y2">
-        <v>0.01825694290847492</v>
+        <v>0.0143329168139992</v>
       </c>
       <c r="Z2">
-        <v>0.2355484864062028</v>
+        <v>0.2256187699466235</v>
       </c>
       <c r="AA2">
-        <v>0.06590354004704167</v>
+        <v>0.04498927609651102</v>
       </c>
       <c r="AB2">
-        <v>0.04730946742339646</v>
+        <v>0.07722245859426692</v>
       </c>
       <c r="AC2">
-        <v>0.01979548613232466</v>
+        <v>-0.02839129950944221</v>
       </c>
       <c r="AD2">
-        <v>17616.393</v>
+        <v>11968.807</v>
       </c>
       <c r="AE2">
-        <v>3.291816815277092</v>
+        <v>2.540327440477001</v>
       </c>
       <c r="AF2">
-        <v>17619.68481681528</v>
+        <v>11971.34732744048</v>
       </c>
       <c r="AG2">
-        <v>16147.16581681528</v>
+        <v>10761.18232744048</v>
       </c>
       <c r="AH2">
-        <v>0.3671747199242647</v>
+        <v>0.3510677846888936</v>
       </c>
       <c r="AI2">
-        <v>0.496598098671254</v>
+        <v>0.4217715012965429</v>
       </c>
       <c r="AJ2">
-        <v>0.3471413168696749</v>
+        <v>0.3271905163455381</v>
       </c>
       <c r="AK2">
-        <v>0.474801365250632</v>
+        <v>0.3960200747522608</v>
       </c>
       <c r="AL2">
-        <v>63.151</v>
+        <v>97.84</v>
       </c>
       <c r="AM2">
-        <v>52.764</v>
+        <v>88.41900000000001</v>
       </c>
       <c r="AN2">
-        <v>7.166064219780434</v>
+        <v>6.468020637041945</v>
       </c>
       <c r="AO2">
-        <v>42.13138350936644</v>
+        <v>23.61112019623876</v>
       </c>
       <c r="AP2">
-        <v>6.568406325332414</v>
+        <v>5.815412461146384</v>
       </c>
       <c r="AQ2">
-        <v>50.42527101811842</v>
+        <v>26.12687318336556</v>
       </c>
     </row>
     <row r="3">
@@ -725,103 +725,118 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.366</v>
+        <v>0.342</v>
       </c>
       <c r="G3">
-        <v>0.758399209486166</v>
+        <v>0.4113263785394933</v>
       </c>
       <c r="H3">
-        <v>0.758399209486166</v>
+        <v>0.4113263785394933</v>
       </c>
       <c r="I3">
-        <v>0.6240118577075099</v>
+        <v>0.3407848981619473</v>
       </c>
       <c r="J3">
-        <v>0.4843904646663304</v>
+        <v>0.3407848981619473</v>
       </c>
       <c r="K3">
-        <v>96.09999999999999</v>
+        <v>-22.3</v>
       </c>
       <c r="L3">
-        <v>0.474802371541502</v>
+        <v>-0.1107799304520616</v>
       </c>
       <c r="M3">
-        <v>99.95099999999999</v>
+        <v>71.41199999999999</v>
       </c>
       <c r="N3">
-        <v>0.01459330422975281</v>
+        <v>0.01886062911021313</v>
       </c>
       <c r="O3">
-        <v>1.040072840790843</v>
+        <v>-3.202331838565022</v>
       </c>
       <c r="P3">
-        <v>99.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.01454205662057789</v>
+        <v>0.01864617172437472</v>
       </c>
       <c r="R3">
-        <v>1.036420395421436</v>
+        <v>-3.165919282511211</v>
       </c>
       <c r="S3">
-        <v>0.3509999999999991</v>
+        <v>0.8119999999999976</v>
       </c>
       <c r="T3">
-        <v>0.003511720743164142</v>
+        <v>0.01137063798801319</v>
       </c>
       <c r="U3">
-        <v>42.9</v>
+        <v>410.1</v>
       </c>
       <c r="V3">
-        <v>0.006263596676935655</v>
+        <v>0.1083115442516441</v>
+      </c>
+      <c r="W3">
+        <v>-0.27909887359199</v>
       </c>
       <c r="X3">
-        <v>0.04761511302274314</v>
+        <v>0.07777910569408637</v>
+      </c>
+      <c r="Y3">
+        <v>-0.3568779792860763</v>
+      </c>
+      <c r="Z3">
+        <v>2.047812817904375</v>
+      </c>
+      <c r="AA3">
+        <v>0.6978636826042727</v>
       </c>
       <c r="AB3">
-        <v>0.04742244877074388</v>
+        <v>0.07725947661324582</v>
+      </c>
+      <c r="AC3">
+        <v>0.6206042059910268</v>
       </c>
       <c r="AD3">
-        <v>61.3</v>
+        <v>62.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>61.3</v>
+        <v>62.5</v>
       </c>
       <c r="AG3">
-        <v>18.4</v>
+        <v>-347.6</v>
       </c>
       <c r="AH3">
-        <v>0.008870687659180365</v>
+        <v>0.01623882768655165</v>
       </c>
       <c r="AI3">
-        <v>0.4341359773371105</v>
+        <v>0.1166697778607429</v>
       </c>
       <c r="AJ3">
-        <v>0.002679286494357481</v>
+        <v>-0.1010847122459069</v>
       </c>
       <c r="AK3">
-        <v>0.1871820956256358</v>
+        <v>-2.76751592356688</v>
       </c>
       <c r="AL3">
-        <v>1.25</v>
+        <v>3.97</v>
       </c>
       <c r="AM3">
-        <v>1.158</v>
+        <v>3.91</v>
       </c>
       <c r="AN3">
-        <v>0.4819182389937107</v>
+        <v>0.9314456035767512</v>
       </c>
       <c r="AO3">
-        <v>101.04</v>
+        <v>17.27959697732997</v>
       </c>
       <c r="AP3">
-        <v>0.1446540880503145</v>
+        <v>-5.180327868852459</v>
       </c>
       <c r="AQ3">
-        <v>109.0673575129534</v>
+        <v>17.54475703324808</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Financière Marjos SA (ENXTPA:FINM)</t>
+          <t>Altamir SCA (ENXTPA:LTA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,89 +855,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.043</v>
+      </c>
+      <c r="E4">
+        <v>0.0694</v>
+      </c>
+      <c r="G4">
+        <v>1.647502356267672</v>
+      </c>
+      <c r="H4">
+        <v>1.647502356267672</v>
+      </c>
+      <c r="I4">
+        <v>0.9392082940622055</v>
+      </c>
+      <c r="J4">
+        <v>0.9392082940622055</v>
+      </c>
       <c r="K4">
-        <v>-1.01</v>
+        <v>161.4</v>
+      </c>
+      <c r="L4">
+        <v>0.760603204524034</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>43.1</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.04283442655535679</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.2670384138785626</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>43.1</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04283442655535679</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.2670384138785626</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.008999999999999999</v>
+        <v>210.6</v>
       </c>
       <c r="V4">
-        <v>0.001761252446183953</v>
+        <v>0.2093023255813953</v>
       </c>
       <c r="W4">
-        <v>-10.30612244897959</v>
+        <v>0.1145330684076072</v>
       </c>
       <c r="X4">
-        <v>0.04740261641241918</v>
+        <v>0.0786283283438169</v>
       </c>
       <c r="Y4">
-        <v>-10.35352506539201</v>
+        <v>0.03590474006379026</v>
       </c>
       <c r="Z4">
-        <v>-0</v>
+        <v>0.1480891130774132</v>
       </c>
       <c r="AA4">
-        <v>6.257668711656442</v>
+        <v>0.1390865232626223</v>
       </c>
       <c r="AB4">
-        <v>0.04740261641241918</v>
+        <v>0.07693277442098963</v>
       </c>
       <c r="AC4">
-        <v>6.210266095244023</v>
+        <v>0.06215374884163267</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="AG4">
-        <v>-0.008999999999999999</v>
+        <v>-164.4</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.04389965792474344</v>
       </c>
       <c r="AI4">
-        <v>-0</v>
+        <v>0.03284515853831935</v>
       </c>
       <c r="AJ4">
-        <v>-0.001764359929425603</v>
+        <v>-0.195295794725588</v>
       </c>
       <c r="AK4">
-        <v>0.009782608695652173</v>
+        <v>-0.1374581939799331</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.454</v>
       </c>
       <c r="AM4">
-        <v>-0.001</v>
+        <v>-2.826</v>
+      </c>
+      <c r="AN4">
+        <v>0.2318113396889112</v>
+      </c>
+      <c r="AO4">
+        <v>438.9867841409692</v>
+      </c>
+      <c r="AP4">
+        <v>-0.8248871048670344</v>
       </c>
       <c r="AQ4">
-        <v>1020</v>
+        <v>-70.52370842179761</v>
       </c>
     </row>
     <row r="5">
@@ -933,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Altamir SCA (ENXTPA:LTA)</t>
+          <t>Tikehau Capital (ENXTPA:TKO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -942,46 +990,49 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.195</v>
+        <v>0.426</v>
       </c>
       <c r="E5">
-        <v>0.211</v>
+        <v>0.24</v>
+      </c>
+      <c r="F5">
+        <v>0.00746</v>
       </c>
       <c r="G5">
-        <v>0.6495275152862701</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.6495275152862701</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.8918843802112284</v>
+        <v>0.6139987827145466</v>
       </c>
       <c r="J5">
-        <v>0.8918843802112284</v>
+        <v>0.5212235903437458</v>
       </c>
       <c r="K5">
-        <v>263.8</v>
+        <v>438.9</v>
       </c>
       <c r="L5">
-        <v>0.7331851028349083</v>
+        <v>0.5342665855143031</v>
       </c>
       <c r="M5">
-        <v>57.3</v>
+        <v>182.8</v>
       </c>
       <c r="N5">
-        <v>0.05435401252134319</v>
+        <v>0.04102241870694105</v>
       </c>
       <c r="O5">
-        <v>0.2172100075815011</v>
+        <v>0.4164957849168376</v>
       </c>
       <c r="P5">
-        <v>57.3</v>
+        <v>182.8</v>
       </c>
       <c r="Q5">
-        <v>0.05435401252134319</v>
+        <v>0.04102241870694105</v>
       </c>
       <c r="R5">
-        <v>0.2172100075815011</v>
+        <v>0.4164957849168376</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -990,73 +1041,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>146.6</v>
+        <v>397.6</v>
       </c>
       <c r="V5">
-        <v>0.1390627964333143</v>
+        <v>0.0892260048024057</v>
       </c>
       <c r="W5">
-        <v>0.233100645047274</v>
+        <v>0.1285212298682284</v>
       </c>
       <c r="X5">
-        <v>0.05123356515368089</v>
+        <v>0.0875225079586924</v>
       </c>
       <c r="Y5">
-        <v>0.1818670798935931</v>
+        <v>0.04099872190953599</v>
       </c>
       <c r="Z5">
-        <v>0.3089979551858496</v>
+        <v>0.2216257048048129</v>
       </c>
       <c r="AA5">
-        <v>0.2755904497474684</v>
+        <v>0.1155165455708277</v>
       </c>
       <c r="AB5">
-        <v>0.04693054861024518</v>
+        <v>0.07776756028288043</v>
       </c>
       <c r="AC5">
-        <v>0.2286599011372233</v>
+        <v>0.0377489852879473</v>
       </c>
       <c r="AD5">
-        <v>170.1</v>
+        <v>1577.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>170.1</v>
+        <v>1577.1</v>
       </c>
       <c r="AG5">
-        <v>23.5</v>
+        <v>1179.5</v>
       </c>
       <c r="AH5">
-        <v>0.1389365351629503</v>
+        <v>0.2614035669296559</v>
       </c>
       <c r="AI5">
-        <v>0.1076854899974677</v>
+        <v>0.3240461073784134</v>
       </c>
       <c r="AJ5">
-        <v>0.02180569731836318</v>
+        <v>0.2092944850592661</v>
       </c>
       <c r="AK5">
-        <v>0.01639916259595255</v>
+        <v>0.2639115745194997</v>
       </c>
       <c r="AL5">
-        <v>13.9</v>
+        <v>8.81</v>
       </c>
       <c r="AM5">
-        <v>7.95</v>
-      </c>
-      <c r="AN5">
-        <v>0.5300716734185105</v>
+        <v>8.81</v>
       </c>
       <c r="AO5">
-        <v>23.0863309352518</v>
-      </c>
-      <c r="AP5">
-        <v>0.0732315363041446</v>
+        <v>57.25312145289443</v>
       </c>
       <c r="AQ5">
-        <v>40.36477987421383</v>
+        <v>57.25312145289443</v>
       </c>
     </row>
     <row r="6">
@@ -1076,121 +1121,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.451</v>
+        <v>-0.0663</v>
       </c>
       <c r="E6">
-        <v>0.501</v>
+        <v>-0.0688</v>
       </c>
       <c r="G6">
-        <v>0.2085505735140772</v>
+        <v>1.673492605233219</v>
       </c>
       <c r="H6">
-        <v>0.2085505735140772</v>
+        <v>1.673492605233219</v>
       </c>
       <c r="I6">
-        <v>0.9186652763295098</v>
+        <v>0.8077360637087599</v>
       </c>
       <c r="J6">
-        <v>0.8864803862012225</v>
+        <v>0.8077360637087599</v>
       </c>
       <c r="K6">
-        <v>168.3</v>
+        <v>75.5</v>
       </c>
       <c r="L6">
-        <v>0.8774765380604796</v>
+        <v>0.8589306029579067</v>
       </c>
       <c r="M6">
-        <v>28.43</v>
+        <v>28.4</v>
       </c>
       <c r="N6">
-        <v>0.0677227251071939</v>
+        <v>0.07713199348180337</v>
       </c>
       <c r="O6">
-        <v>0.1689245395127748</v>
+        <v>0.376158940397351</v>
       </c>
       <c r="P6">
-        <v>19.1</v>
+        <v>28.4</v>
       </c>
       <c r="Q6">
-        <v>0.04549785612196284</v>
+        <v>0.07713199348180337</v>
       </c>
       <c r="R6">
-        <v>0.1134878193701723</v>
+        <v>0.376158940397351</v>
       </c>
       <c r="S6">
-        <v>9.329999999999998</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.3281744635947942</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>37</v>
+        <v>17.2</v>
       </c>
       <c r="V6">
-        <v>0.08813720819437827</v>
+        <v>0.04671374253123303</v>
       </c>
       <c r="W6">
-        <v>0.3234672304439747</v>
+        <v>0.1102833771545428</v>
       </c>
       <c r="X6">
-        <v>0.05318834742565883</v>
+        <v>0.0811139926018983</v>
       </c>
       <c r="Y6">
-        <v>0.2702788830183159</v>
+        <v>0.02916938455264449</v>
       </c>
       <c r="Z6">
-        <v>0.3037694013303769</v>
+        <v>0.1172156287505001</v>
       </c>
       <c r="AA6">
-        <v>0.2692856162074667</v>
+        <v>0.09467929057207627</v>
       </c>
       <c r="AB6">
-        <v>0.04673686843398735</v>
+        <v>0.07632056557577317</v>
       </c>
       <c r="AC6">
-        <v>0.2225487477734794</v>
+        <v>0.0183587249963031</v>
       </c>
       <c r="AD6">
-        <v>102.3</v>
+        <v>48.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>102.3</v>
+        <v>48.6</v>
       </c>
       <c r="AG6">
-        <v>65.3</v>
+        <v>31.4</v>
       </c>
       <c r="AH6">
-        <v>0.1959394751963225</v>
+        <v>0.1166026871401152</v>
       </c>
       <c r="AI6">
-        <v>0.130003812428517</v>
+        <v>0.0694980694980695</v>
       </c>
       <c r="AJ6">
-        <v>0.134611420325706</v>
+        <v>0.07857857857857858</v>
       </c>
       <c r="AK6">
-        <v>0.08707827710361381</v>
+        <v>0.04603430582026096</v>
       </c>
       <c r="AL6">
-        <v>1.8</v>
+        <v>0.973</v>
       </c>
       <c r="AM6">
-        <v>1.8</v>
+        <v>0.973</v>
       </c>
       <c r="AN6">
-        <v>0.5802609188882586</v>
+        <v>0.6797202797202797</v>
       </c>
       <c r="AO6">
-        <v>97.88888888888889</v>
+        <v>72.97019527235355</v>
       </c>
       <c r="AP6">
-        <v>0.3703913783323879</v>
+        <v>0.4391608391608392</v>
       </c>
       <c r="AQ6">
-        <v>97.88888888888889</v>
+        <v>72.97019527235355</v>
       </c>
     </row>
     <row r="7">
@@ -1210,46 +1255,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0161</v>
+        <v>-0.0226</v>
       </c>
       <c r="E7">
-        <v>-0.169</v>
+        <v>-0.263</v>
       </c>
       <c r="G7">
-        <v>0.06972607612949128</v>
+        <v>0.1154606563859233</v>
       </c>
       <c r="H7">
-        <v>0.06972607612949128</v>
+        <v>0.1154606563859233</v>
       </c>
       <c r="I7">
-        <v>0.07719672714336534</v>
+        <v>0.05140371688414393</v>
       </c>
       <c r="J7">
-        <v>0.05258042384509833</v>
+        <v>0.03334295149241769</v>
       </c>
       <c r="K7">
-        <v>13.3</v>
+        <v>7.16</v>
       </c>
       <c r="L7">
-        <v>0.04731412308786909</v>
+        <v>0.02831158560695927</v>
       </c>
       <c r="M7">
-        <v>0.96</v>
+        <v>62.7</v>
       </c>
       <c r="N7">
-        <v>0.003244339303818858</v>
+        <v>0.1714520098441346</v>
       </c>
       <c r="O7">
-        <v>0.07218045112781954</v>
+        <v>8.756983240223464</v>
       </c>
       <c r="P7">
-        <v>0.96</v>
+        <v>62.7</v>
       </c>
       <c r="Q7">
-        <v>0.003244339303818858</v>
+        <v>0.1714520098441346</v>
       </c>
       <c r="R7">
-        <v>0.07218045112781954</v>
+        <v>8.756983240223464</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1258,73 +1303,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>97.7</v>
+        <v>120.4</v>
       </c>
       <c r="V7">
-        <v>0.3301791145657317</v>
+        <v>0.3292316106097894</v>
       </c>
       <c r="W7">
-        <v>0.07139023081052066</v>
+        <v>0.03468992248062015</v>
       </c>
       <c r="X7">
-        <v>0.04877468614671959</v>
+        <v>0.07820261941564596</v>
       </c>
       <c r="Y7">
-        <v>0.02261554466380107</v>
+        <v>-0.04351269693502581</v>
       </c>
       <c r="Z7">
-        <v>4.004273504273503</v>
+        <v>2.01033386327504</v>
       </c>
       <c r="AA7">
-        <v>0.210546398046398</v>
+        <v>0.06703046448674431</v>
       </c>
       <c r="AB7">
-        <v>0.04721699003525619</v>
+        <v>0.07722245859426692</v>
       </c>
       <c r="AC7">
-        <v>0.1633294080111418</v>
+        <v>-0.01019199410752261</v>
       </c>
       <c r="AD7">
-        <v>17.1</v>
+        <v>11.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>17.1</v>
+        <v>11.4</v>
       </c>
       <c r="AG7">
-        <v>-80.59999999999999</v>
+        <v>-109</v>
       </c>
       <c r="AH7">
-        <v>0.05463258785942492</v>
+        <v>0.03023070803500398</v>
       </c>
       <c r="AI7">
-        <v>0.07651006711409397</v>
+        <v>0.0782967032967033</v>
       </c>
       <c r="AJ7">
-        <v>-0.3743613562470971</v>
+        <v>-0.4246201791975068</v>
       </c>
       <c r="AK7">
-        <v>-0.6406995230524641</v>
+        <v>-4.325396825396827</v>
       </c>
       <c r="AL7">
-        <v>0.366</v>
+        <v>0.652</v>
       </c>
       <c r="AM7">
-        <v>0.366</v>
+        <v>0.652</v>
       </c>
       <c r="AN7">
-        <v>0.534375</v>
+        <v>0.5728643216080402</v>
       </c>
       <c r="AO7">
-        <v>59.2896174863388</v>
+        <v>19.93865030674846</v>
       </c>
       <c r="AP7">
-        <v>-2.51875</v>
+        <v>-5.477386934673367</v>
       </c>
       <c r="AQ7">
-        <v>59.2896174863388</v>
+        <v>19.93865030674846</v>
       </c>
     </row>
     <row r="8">
@@ -1335,7 +1380,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tikehau Capital (ENXTPA:TKO)</t>
+          <t>Amundi S.A. (ENXTPA:AMUN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1344,115 +1389,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.621</v>
+        <v>0.156</v>
       </c>
       <c r="E8">
-        <v>0.49</v>
+        <v>0.134</v>
+      </c>
+      <c r="F8">
+        <v>-0.00252</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.3296965918536991</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.3296965918536991</v>
       </c>
       <c r="I8">
-        <v>0.4715909090909091</v>
+        <v>0.2526842615683015</v>
       </c>
       <c r="J8">
-        <v>0.4653769561184158</v>
+        <v>0.2083465343251663</v>
       </c>
       <c r="K8">
-        <v>221.7</v>
+        <v>1070.3</v>
       </c>
       <c r="L8">
-        <v>0.406341642228739</v>
+        <v>0.1853525907453588</v>
       </c>
       <c r="M8">
-        <v>79.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.01742259671296601</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.3581416328371674</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>79.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.01742259671296601</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.3581416328371674</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>1030.3</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>0.2260768437452</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>0.07076284711139483</v>
+        <v>0.09296124515781611</v>
       </c>
       <c r="X8">
-        <v>0.05687134875771911</v>
+        <v>0.1024759555439966</v>
       </c>
       <c r="Y8">
-        <v>0.01389149835367572</v>
+        <v>-0.009514710386180514</v>
       </c>
       <c r="Z8">
-        <v>0.1743576633005241</v>
+        <v>0.2159348426036034</v>
       </c>
       <c r="AA8">
-        <v>0.0811420386227175</v>
+        <v>0.04498927609651102</v>
       </c>
       <c r="AB8">
-        <v>0.04643390197712133</v>
+        <v>0.07338057560595324</v>
       </c>
       <c r="AC8">
-        <v>0.03470813664559617</v>
+        <v>-0.02839129950944221</v>
       </c>
       <c r="AD8">
-        <v>1817.5</v>
+        <v>10053.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1817.5</v>
+        <v>10053.6</v>
       </c>
       <c r="AG8">
-        <v>787.2</v>
+        <v>10053.6</v>
       </c>
       <c r="AH8">
-        <v>0.2851069837485097</v>
+        <v>0.4657420018345054</v>
       </c>
       <c r="AI8">
-        <v>0.3468511450381679</v>
+        <v>0.493702028609732</v>
       </c>
       <c r="AJ8">
-        <v>0.147291608195341</v>
+        <v>0.4657420018345054</v>
       </c>
       <c r="AK8">
-        <v>0.1869966981020025</v>
+        <v>0.493702028609732</v>
       </c>
       <c r="AL8">
-        <v>29.1</v>
+        <v>78.5</v>
       </c>
       <c r="AM8">
-        <v>29.1</v>
+        <v>78.5</v>
+      </c>
+      <c r="AN8">
+        <v>6.727966271832965</v>
       </c>
       <c r="AO8">
-        <v>8.84192439862543</v>
+        <v>18.58726114649681</v>
+      </c>
+      <c r="AP8">
+        <v>6.727966271832965</v>
       </c>
       <c r="AQ8">
-        <v>8.84192439862543</v>
+        <v>18.58726114649681</v>
       </c>
     </row>
     <row r="9">
@@ -1463,7 +1514,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amundi SA (ENXTPA:AMUN)</t>
+          <t>Societe de Tayninh SA (ENXTPA:TAYN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1471,32 +1522,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.127</v>
-      </c>
-      <c r="E9">
-        <v>0.2</v>
-      </c>
-      <c r="F9">
-        <v>0.121</v>
-      </c>
-      <c r="G9">
-        <v>0.252553575005007</v>
-      </c>
-      <c r="H9">
-        <v>0.252553575005007</v>
-      </c>
-      <c r="I9">
-        <v>0.2974664530342479</v>
-      </c>
-      <c r="J9">
-        <v>0.2287258228611435</v>
-      </c>
       <c r="K9">
-        <v>1554</v>
-      </c>
-      <c r="L9">
-        <v>0.2593631083516924</v>
+        <v>-0.099</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1505,7 +1532,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1514,79 +1541,70 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>8.47457627118644e-05</v>
       </c>
       <c r="W9">
-        <v>0.1430662579059298</v>
+        <v>-0.004876847290640394</v>
       </c>
       <c r="X9">
-        <v>0.06904905367662002</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="Y9">
-        <v>0.07401720422930975</v>
+        <v>-0.08217928662344393</v>
       </c>
       <c r="Z9">
-        <v>0.2215099320120227</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>0.05066504147136585</v>
+        <v>-0.005369458128078817</v>
       </c>
       <c r="AB9">
-        <v>0.04578220585231271</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AC9">
-        <v>0.004882835619053144</v>
+        <v>-0.08267189746088235</v>
       </c>
       <c r="AD9">
-        <v>15228</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>15228</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>15228</v>
+        <v>-0.001</v>
       </c>
       <c r="AH9">
-        <v>0.4769107906233852</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>0.5681601952071278</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>0.4769107906233852</v>
+        <v>-8.475294516484447e-05</v>
       </c>
       <c r="AK9">
-        <v>0.5681601952071278</v>
+        <v>-5.618293162537222e-05</v>
       </c>
       <c r="AL9">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>10.9</v>
-      </c>
-      <c r="AN9">
-        <v>8.3900826446281</v>
-      </c>
-      <c r="AO9">
-        <v>163.5137614678899</v>
-      </c>
-      <c r="AP9">
-        <v>8.3900826446281</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="AQ9">
-        <v>163.5137614678899</v>
+        <v>12.11111111111111</v>
       </c>
     </row>
     <row r="10">
@@ -1597,7 +1615,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NextStage - S.C.A. (ENXTPA:NEXTS)</t>
+          <t>Compagnie Lebon (ENXTPA:ALBON)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1605,107 +1623,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.0271</v>
+      </c>
+      <c r="E10">
+        <v>-0.147</v>
+      </c>
       <c r="G10">
-        <v>-0</v>
+        <v>-0.04625</v>
       </c>
       <c r="H10">
-        <v>-0</v>
+        <v>-0.04625</v>
       </c>
       <c r="I10">
-        <v>24.125</v>
+        <v>-0.02583543169821402</v>
       </c>
       <c r="J10">
-        <v>24.125</v>
+        <v>-0.02583543169821402</v>
       </c>
       <c r="K10">
-        <v>-6.63</v>
+        <v>8.99</v>
       </c>
       <c r="L10">
-        <v>27.625</v>
+        <v>0.07491666666666667</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>2.901</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.02797492767598843</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>0.3226918798665184</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>2.87</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.02767598842815815</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>0.3192436040044494</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>0.03100000000000014</v>
+      </c>
+      <c r="T10">
+        <v>0.01068597035505003</v>
       </c>
       <c r="U10">
-        <v>35.5</v>
+        <v>53.4</v>
       </c>
       <c r="V10">
-        <v>0.1632183908045977</v>
+        <v>0.5149469623915139</v>
       </c>
       <c r="W10">
-        <v>-0.0247295785154793</v>
+        <v>0.04716684155299056</v>
       </c>
       <c r="X10">
-        <v>0.04740731031674891</v>
+        <v>0.1246335007264621</v>
       </c>
       <c r="Y10">
-        <v>-0.0721368888322282</v>
+        <v>-0.07746665917347156</v>
       </c>
       <c r="Z10">
-        <v>-0.0009638554216867468</v>
+        <v>0.5410980689330799</v>
       </c>
       <c r="AA10">
-        <v>-0.02325301204819277</v>
+        <v>-0.01397950220195609</v>
       </c>
       <c r="AB10">
-        <v>0.04740194481153672</v>
+        <v>0.07207253921301257</v>
       </c>
       <c r="AC10">
-        <v>-0.07065495685972949</v>
+        <v>-0.08605204141496865</v>
       </c>
       <c r="AD10">
-        <v>0.043</v>
+        <v>167.5</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>2.471259018928411</v>
       </c>
       <c r="AF10">
-        <v>0.043</v>
+        <v>169.9712590189284</v>
       </c>
       <c r="AG10">
-        <v>-35.457</v>
+        <v>116.5712590189284</v>
       </c>
       <c r="AH10">
-        <v>0.0001976620714065725</v>
+        <v>0.6210782222007916</v>
       </c>
       <c r="AI10">
-        <v>0.0001575420509044013</v>
+        <v>0.4870637756724517</v>
       </c>
       <c r="AJ10">
-        <v>-0.1947726636014568</v>
+        <v>0.5292168371767066</v>
       </c>
       <c r="AK10">
-        <v>-0.1493284704118462</v>
+        <v>0.3943930793740104</v>
       </c>
       <c r="AL10">
-        <v>0.78</v>
+        <v>4.43</v>
       </c>
       <c r="AM10">
-        <v>0.78</v>
+        <v>4.322</v>
+      </c>
+      <c r="AN10">
+        <v>552.8052805280528</v>
       </c>
       <c r="AO10">
-        <v>-7.423076923076922</v>
+        <v>-0.6139954853273139</v>
+      </c>
+      <c r="AP10">
+        <v>384.7236271251763</v>
       </c>
       <c r="AQ10">
-        <v>-7.423076923076922</v>
+        <v>-0.6293382693197594</v>
       </c>
     </row>
     <row r="11">
@@ -1716,7 +1749,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Compagnie Lebon (ENXTPA:LBON)</t>
+          <t>Idsud S.A. (ENXTPA:ALIDS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1725,121 +1758,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0101</v>
+        <v>-0.0382</v>
       </c>
       <c r="E11">
-        <v>-0.104</v>
+        <v>1.026</v>
       </c>
       <c r="G11">
-        <v>-0.1086261980830671</v>
+        <v>-2.623529411764706</v>
       </c>
       <c r="H11">
-        <v>-0.1086261980830671</v>
+        <v>-2.623529411764706</v>
       </c>
       <c r="I11">
-        <v>-0.1576881791044028</v>
+        <v>-2.585663158011433</v>
       </c>
       <c r="J11">
-        <v>-0.1576881791044028</v>
+        <v>-2.467486800617784</v>
       </c>
       <c r="K11">
-        <v>10.8</v>
+        <v>55.5</v>
       </c>
       <c r="L11">
-        <v>0.1150159744408946</v>
+        <v>65.29411764705883</v>
       </c>
       <c r="M11">
-        <v>1.731</v>
+        <v>0.8514999999999999</v>
       </c>
       <c r="N11">
-        <v>0.01645437262357415</v>
+        <v>0.01166438356164383</v>
       </c>
       <c r="O11">
-        <v>0.1602777777777778</v>
+        <v>0.01534234234234234</v>
       </c>
       <c r="P11">
-        <v>0.421</v>
+        <v>0.6435</v>
       </c>
       <c r="Q11">
-        <v>0.004001901140684411</v>
+        <v>0.008815068493150684</v>
       </c>
       <c r="R11">
-        <v>0.03898148148148148</v>
+        <v>0.01159459459459459</v>
       </c>
       <c r="S11">
-        <v>1.31</v>
+        <v>0.208</v>
       </c>
       <c r="T11">
-        <v>0.756787983824379</v>
+        <v>0.2442748091603053</v>
       </c>
       <c r="U11">
-        <v>76.8</v>
+        <v>0.863</v>
       </c>
       <c r="V11">
-        <v>0.7300380228136881</v>
+        <v>0.01182191780821918</v>
       </c>
       <c r="W11">
-        <v>0.06268136970400465</v>
+        <v>2.875647668393782</v>
       </c>
       <c r="X11">
-        <v>0.09713184374132687</v>
+        <v>0.07799827931755962</v>
       </c>
       <c r="Y11">
-        <v>-0.03445047403732222</v>
+        <v>2.797649389076223</v>
       </c>
       <c r="Z11">
-        <v>0.3954606673076562</v>
+        <v>0.05148685427280263</v>
       </c>
       <c r="AA11">
-        <v>-0.06235947253515632</v>
+        <v>-0.1270431333234718</v>
       </c>
       <c r="AB11">
-        <v>0.04510287062628385</v>
+        <v>0.07724018695528731</v>
       </c>
       <c r="AC11">
-        <v>-0.1074623431614402</v>
+        <v>-0.2042833202787591</v>
       </c>
       <c r="AD11">
-        <v>217.2</v>
+        <v>1.69</v>
       </c>
       <c r="AE11">
-        <v>3.144600089517098</v>
+        <v>0.06906842154859023</v>
       </c>
       <c r="AF11">
-        <v>220.3446000895171</v>
+        <v>1.75906842154859</v>
       </c>
       <c r="AG11">
-        <v>143.5446000895171</v>
+        <v>0.8960684215485901</v>
       </c>
       <c r="AH11">
-        <v>0.676849193717013</v>
+        <v>0.02352983335251881</v>
       </c>
       <c r="AI11">
-        <v>0.5335936104788666</v>
+        <v>-3.816333060664936</v>
       </c>
       <c r="AJ11">
-        <v>0.5770762462295017</v>
+        <v>0.01212606354693818</v>
       </c>
       <c r="AK11">
-        <v>0.4270322951827588</v>
+        <v>-0.6768238148656539</v>
       </c>
       <c r="AL11">
-        <v>4.98</v>
+        <v>0.051</v>
       </c>
       <c r="AM11">
-        <v>4.805000000000001</v>
+        <v>-4.548999999999999</v>
       </c>
       <c r="AN11">
-        <v>-20.34088780670537</v>
+        <v>-0.8693415637860082</v>
       </c>
       <c r="AO11">
-        <v>-2.8714859437751</v>
+        <v>-43.92156862745099</v>
       </c>
       <c r="AP11">
-        <v>-13.44302304640542</v>
+        <v>-0.4609405460640896</v>
       </c>
       <c r="AQ11">
-        <v>-2.976066597294485</v>
+        <v>0.4924159155858431</v>
       </c>
     </row>
     <row r="12">
@@ -1850,7 +1883,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Idsud S.A. (ENXTPA:ALIDS)</t>
+          <t>Société des Chemins de Fer et Tramways du Var et du Gard (ENXTPA:MLCVG)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1858,119 +1891,74 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D12">
-        <v>-0.116</v>
-      </c>
       <c r="E12">
-        <v>0.265</v>
-      </c>
-      <c r="G12">
-        <v>-3.650546021840873</v>
-      </c>
-      <c r="H12">
-        <v>-3.650546021840873</v>
-      </c>
-      <c r="I12">
-        <v>-4.198819571219967</v>
-      </c>
-      <c r="J12">
-        <v>-3.181139573449704</v>
+        <v>-0.124</v>
       </c>
       <c r="K12">
-        <v>0.899</v>
-      </c>
-      <c r="L12">
-        <v>1.402496099843994</v>
+        <v>1.24</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>0.7875</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.001865671641791045</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.6350806451612903</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>0.7875</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.001865671641791045</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.6350806451612903</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>0.06042328042328042</v>
-      </c>
-      <c r="W12">
-        <v>0.05137142857142857</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>0.04815564485173005</v>
-      </c>
-      <c r="Y12">
-        <v>0.003215783719698523</v>
-      </c>
-      <c r="Z12">
-        <v>0.03667632038087726</v>
-      </c>
-      <c r="AA12">
-        <v>-0.1166724941721285</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AB12">
-        <v>0.0474025050483286</v>
-      </c>
-      <c r="AC12">
-        <v>-0.1640749992204572</v>
+        <v>0.07730243933280354</v>
       </c>
       <c r="AD12">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>0.1472167257599941</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.997216725759994</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>-2.712783274240006</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>0.03074156192776826</v>
-      </c>
-      <c r="AI12">
-        <v>0.1344211146450986</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>-0.02955513165134101</v>
-      </c>
-      <c r="AK12">
-        <v>-0.1635466226245809</v>
+        <v>0</v>
       </c>
       <c r="AL12">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>-4.051</v>
-      </c>
-      <c r="AN12">
-        <v>-1.186511240632806</v>
-      </c>
-      <c r="AO12">
-        <v>-46.4406779661017</v>
-      </c>
-      <c r="AP12">
-        <v>1.129385209925065</v>
+        <v>-1.36</v>
       </c>
       <c r="AQ12">
-        <v>0.6763762034065663</v>
+        <v>0.07720588235294117</v>
       </c>
     </row>
     <row r="13">
@@ -1981,7 +1969,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Compagnie des Tramways de Rouen (ENXTPA:MLTRA)</t>
+          <t>Financière Marjos SA (ENXTPA:FINM)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1990,159 +1978,79 @@
         </is>
       </c>
       <c r="K13">
-        <v>-0.016</v>
+        <v>-0.034</v>
       </c>
       <c r="M13">
-        <v>0.4131</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.007959537572254335</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>-25.81875</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>0.4131</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.007959537572254335</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>-25.81875</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>0.0003610108303249097</v>
+      </c>
+      <c r="W13">
+        <v>0.03732162458836444</v>
       </c>
       <c r="X13">
-        <v>0.04740261641241918</v>
+        <v>0.07956463139107567</v>
+      </c>
+      <c r="Y13">
+        <v>-0.04224300680271123</v>
       </c>
       <c r="AB13">
-        <v>0.04740261641241918</v>
+        <v>0.0771102356953756</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>0.07264814194844325</v>
+      </c>
+      <c r="AI13">
+        <v>-0.35</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>0.07233757535164098</v>
+      </c>
+      <c r="AK13">
+        <v>-0.3478260869565217</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-0.024</v>
+        <v>-0.004</v>
       </c>
       <c r="AQ13">
-        <v>1.666666666666667</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Courbet Sa (ENXTPA:MLCOU)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K14">
-        <v>-0.151</v>
-      </c>
-      <c r="M14">
-        <v>-0</v>
-      </c>
-      <c r="N14">
-        <v>-0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>-0</v>
-      </c>
-      <c r="Q14">
-        <v>-0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0.04740261641241918</v>
-      </c>
-      <c r="AB14">
-        <v>0.04740261641241918</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0.016</v>
-      </c>
-      <c r="AM14">
-        <v>-0.019</v>
-      </c>
-      <c r="AN14">
-        <v>-0</v>
-      </c>
-      <c r="AO14">
-        <v>-10.6875</v>
-      </c>
-      <c r="AP14">
-        <v>-0</v>
-      </c>
-      <c r="AQ14">
-        <v>9</v>
+        <v>28.5</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/france/france_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0271</v>
+        <v>0.0507</v>
       </c>
       <c r="E2">
-        <v>0.0003000000000000017</v>
+        <v>-0.00416</v>
       </c>
       <c r="F2">
-        <v>0.00746</v>
+        <v>0.108</v>
       </c>
       <c r="G2">
-        <v>0.3352567577515878</v>
+        <v>0.2368913584249027</v>
       </c>
       <c r="H2">
-        <v>0.3352567577515878</v>
+        <v>0.2368913584249027</v>
       </c>
       <c r="I2">
-        <v>0.3091632279949812</v>
+        <v>0.2679837575736048</v>
       </c>
       <c r="J2">
-        <v>0.2885104865689745</v>
+        <v>0.2258948440110659</v>
       </c>
       <c r="K2">
-        <v>1796.557</v>
+        <v>1484.286</v>
       </c>
       <c r="L2">
-        <v>0.2404691442300614</v>
+        <v>0.198827625284822</v>
       </c>
       <c r="M2">
-        <v>392.952</v>
+        <v>184.1679</v>
       </c>
       <c r="N2">
-        <v>0.01775775731444605</v>
+        <v>0.008294244808438005</v>
       </c>
       <c r="O2">
-        <v>0.2187250390608258</v>
+        <v>0.1240784457981818</v>
       </c>
       <c r="P2">
-        <v>391.901</v>
+        <v>183.6209</v>
       </c>
       <c r="Q2">
-        <v>0.01771026193857958</v>
+        <v>0.008269609940416946</v>
       </c>
       <c r="R2">
-        <v>0.2181400311818662</v>
+        <v>0.1237099184388992</v>
       </c>
       <c r="S2">
-        <v>1.050999999999998</v>
+        <v>0.5469999999999957</v>
       </c>
       <c r="T2">
-        <v>0.002674626926443937</v>
+        <v>0.002970115856237682</v>
       </c>
       <c r="U2">
-        <v>1210.165</v>
+        <v>991.12</v>
       </c>
       <c r="V2">
-        <v>0.05468814608511117</v>
+        <v>0.04463639925599996</v>
       </c>
       <c r="W2">
-        <v>0.09296124515781611</v>
+        <v>0.04670329670329671</v>
       </c>
       <c r="X2">
-        <v>0.0786283283438169</v>
+        <v>0.07105980382206908</v>
       </c>
       <c r="Y2">
-        <v>0.0143329168139992</v>
+        <v>-0.02435650711877237</v>
       </c>
       <c r="Z2">
-        <v>0.2256187699466235</v>
+        <v>0.2812914767196815</v>
       </c>
       <c r="AA2">
-        <v>0.04498927609651102</v>
+        <v>0.03691335048393073</v>
       </c>
       <c r="AB2">
-        <v>0.07722245859426692</v>
+        <v>0.06575166718052612</v>
       </c>
       <c r="AC2">
-        <v>-0.02839129950944221</v>
+        <v>-0.02722825893354664</v>
       </c>
       <c r="AD2">
-        <v>11968.807</v>
+        <v>20433.92</v>
       </c>
       <c r="AE2">
-        <v>2.540327440477001</v>
+        <v>0.006663995507069127</v>
       </c>
       <c r="AF2">
-        <v>11971.34732744048</v>
+        <v>20433.92666399551</v>
       </c>
       <c r="AG2">
-        <v>10761.18232744048</v>
+        <v>19442.80666399551</v>
       </c>
       <c r="AH2">
-        <v>0.3510677846888936</v>
+        <v>0.479239599362848</v>
       </c>
       <c r="AI2">
-        <v>0.4217715012965429</v>
+        <v>0.5464357999040991</v>
       </c>
       <c r="AJ2">
-        <v>0.3271905163455381</v>
+        <v>0.4668465163944769</v>
       </c>
       <c r="AK2">
-        <v>0.3960200747522608</v>
+        <v>0.5340871860860927</v>
       </c>
       <c r="AL2">
-        <v>97.84</v>
+        <v>69.22200000000001</v>
       </c>
       <c r="AM2">
-        <v>88.41900000000001</v>
+        <v>52.20700000000001</v>
       </c>
       <c r="AN2">
-        <v>6.468020637041945</v>
+        <v>11.81115943335807</v>
       </c>
       <c r="AO2">
-        <v>23.61112019623876</v>
+        <v>28.90040738493542</v>
       </c>
       <c r="AP2">
-        <v>5.815412461146384</v>
+        <v>11.23827877080892</v>
       </c>
       <c r="AQ2">
-        <v>26.12687318336556</v>
+        <v>38.31945907636906</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Antin Infrastructure Partners S.A. (ENXTPA:ANTIN)</t>
+          <t>Antin Infrastructure Partners SAS (ENXTPA:ANTIN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,118 +725,118 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.342</v>
+        <v>0.259</v>
       </c>
       <c r="G3">
-        <v>0.4113263785394933</v>
+        <v>0.4107972828030033</v>
       </c>
       <c r="H3">
-        <v>0.4113263785394933</v>
+        <v>0.4107972828030033</v>
       </c>
       <c r="I3">
-        <v>0.3407848981619473</v>
+        <v>0.7343582409724706</v>
       </c>
       <c r="J3">
-        <v>0.3407848981619473</v>
+        <v>0.3671791204862353</v>
       </c>
       <c r="K3">
-        <v>-22.3</v>
+        <v>22.1</v>
       </c>
       <c r="L3">
-        <v>-0.1107799304520616</v>
+        <v>0.07901322845906329</v>
       </c>
       <c r="M3">
-        <v>71.41199999999999</v>
+        <v>80.514</v>
       </c>
       <c r="N3">
-        <v>0.01886062911021313</v>
+        <v>0.02957898603967671</v>
       </c>
       <c r="O3">
-        <v>-3.202331838565022</v>
+        <v>3.643167420814479</v>
       </c>
       <c r="P3">
-        <v>70.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="Q3">
-        <v>0.01864617172437472</v>
+        <v>0.02939015429831007</v>
       </c>
       <c r="R3">
-        <v>-3.165919282511211</v>
+        <v>3.619909502262443</v>
       </c>
       <c r="S3">
-        <v>0.8119999999999976</v>
+        <v>0.5139999999999958</v>
       </c>
       <c r="T3">
-        <v>0.01137063798801319</v>
+        <v>0.006383982909804454</v>
       </c>
       <c r="U3">
-        <v>410.1</v>
+        <v>464</v>
       </c>
       <c r="V3">
-        <v>0.1083115442516441</v>
+        <v>0.1704628949301984</v>
       </c>
       <c r="W3">
-        <v>-0.27909887359199</v>
+        <v>0.04670329670329671</v>
       </c>
       <c r="X3">
-        <v>0.07777910569408637</v>
+        <v>0.06647452759685629</v>
       </c>
       <c r="Y3">
-        <v>-0.3568779792860763</v>
+        <v>-0.01977123089355958</v>
       </c>
       <c r="Z3">
-        <v>2.047812817904375</v>
+        <v>2.226910828025477</v>
       </c>
       <c r="AA3">
-        <v>0.6978636826042727</v>
+        <v>0.8176751592356687</v>
       </c>
       <c r="AB3">
-        <v>0.07725947661324582</v>
+        <v>0.06591972010222516</v>
       </c>
       <c r="AC3">
-        <v>0.6206042059910268</v>
+        <v>0.7517554391334436</v>
       </c>
       <c r="AD3">
-        <v>62.5</v>
+        <v>63.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>62.5</v>
+        <v>63.6</v>
       </c>
       <c r="AG3">
-        <v>-347.6</v>
+        <v>-400.4</v>
       </c>
       <c r="AH3">
-        <v>0.01623882768655165</v>
+        <v>0.02283170591614015</v>
       </c>
       <c r="AI3">
-        <v>0.1166697778607429</v>
+        <v>0.1076142131979695</v>
       </c>
       <c r="AJ3">
-        <v>-0.1010847122459069</v>
+        <v>-0.1724672639558925</v>
       </c>
       <c r="AK3">
-        <v>-2.76751592356688</v>
+        <v>-3.152755905511811</v>
       </c>
       <c r="AL3">
-        <v>3.97</v>
+        <v>2.51</v>
       </c>
       <c r="AM3">
-        <v>3.91</v>
+        <v>-4.470000000000001</v>
       </c>
       <c r="AN3">
-        <v>0.9314456035767512</v>
+        <v>0.3097905504140283</v>
       </c>
       <c r="AO3">
-        <v>17.27959697732997</v>
+        <v>81.83266932270918</v>
       </c>
       <c r="AP3">
-        <v>-5.180327868852459</v>
+        <v>-1.950316609839259</v>
       </c>
       <c r="AQ3">
-        <v>17.54475703324808</v>
+        <v>-45.95078299776286</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Altamir SCA (ENXTPA:LTA)</t>
+          <t>IDI (ENXTPA:IDIP)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,121 +856,106 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.043</v>
+        <v>0.0134</v>
       </c>
       <c r="E4">
-        <v>0.0694</v>
+        <v>-0.00416</v>
       </c>
       <c r="G4">
-        <v>1.647502356267672</v>
+        <v>0.512883435582822</v>
       </c>
       <c r="H4">
-        <v>1.647502356267672</v>
+        <v>0.512883435582822</v>
       </c>
       <c r="I4">
-        <v>0.9392082940622055</v>
+        <v>0.8625766871165644</v>
       </c>
       <c r="J4">
-        <v>0.9392082940622055</v>
+        <v>0.8625766871165644</v>
       </c>
       <c r="K4">
-        <v>161.4</v>
+        <v>139.5</v>
       </c>
       <c r="L4">
-        <v>0.760603204524034</v>
+        <v>0.8558282208588958</v>
       </c>
       <c r="M4">
-        <v>43.1</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04283442655535679</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.2670384138785626</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>43.1</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04283442655535679</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2670384138785626</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>210.6</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.2093023255813953</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>0.1145330684076072</v>
+        <v>0.2143845089903181</v>
       </c>
       <c r="X4">
-        <v>0.0786283283438169</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="Y4">
-        <v>0.03590474006379026</v>
+        <v>0.1483865943718963</v>
       </c>
       <c r="Z4">
-        <v>0.1480891130774132</v>
+        <v>0.2389678932707814</v>
       </c>
       <c r="AA4">
-        <v>0.1390865232626223</v>
+        <v>0.2061281337047354</v>
       </c>
       <c r="AB4">
-        <v>0.07693277442098963</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AC4">
-        <v>0.06215374884163267</v>
+        <v>0.1401302190863136</v>
       </c>
       <c r="AD4">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-164.4</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.04389965792474344</v>
-      </c>
-      <c r="AI4">
-        <v>0.03284515853831935</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.195295794725588</v>
-      </c>
-      <c r="AK4">
-        <v>-0.1374581939799331</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>0.454</v>
+        <v>3.46</v>
       </c>
       <c r="AM4">
-        <v>-2.826</v>
-      </c>
-      <c r="AN4">
-        <v>0.2318113396889112</v>
+        <v>3.46</v>
       </c>
       <c r="AO4">
-        <v>438.9867841409692</v>
-      </c>
-      <c r="AP4">
-        <v>-0.8248871048670344</v>
+        <v>40.63583815028902</v>
       </c>
       <c r="AQ4">
-        <v>-70.52370842179761</v>
+        <v>40.63583815028902</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tikehau Capital (ENXTPA:TKO)</t>
+          <t>Amundi S.A. (ENXTPA:AMUN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,118 +975,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.426</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="E5">
-        <v>0.24</v>
+        <v>0.08039999999999999</v>
       </c>
       <c r="F5">
-        <v>0.00746</v>
+        <v>0.0355</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.2471371336635225</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.2471371336635225</v>
       </c>
       <c r="I5">
-        <v>0.6139987827145466</v>
+        <v>0.2266317549449509</v>
       </c>
       <c r="J5">
-        <v>0.5212235903437458</v>
+        <v>0.174073425433095</v>
       </c>
       <c r="K5">
-        <v>438.9</v>
+        <v>1173.5</v>
       </c>
       <c r="L5">
-        <v>0.5342665855143031</v>
+        <v>0.185100476355721</v>
       </c>
       <c r="M5">
-        <v>182.8</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.04102241870694105</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.4164957849168376</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>182.8</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.04102241870694105</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4164957849168376</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>397.6</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.0892260048024057</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>0.1285212298682284</v>
+        <v>0.1144610042526628</v>
       </c>
       <c r="X5">
-        <v>0.0875225079586924</v>
+        <v>0.09299207912353957</v>
       </c>
       <c r="Y5">
-        <v>0.04099872190953599</v>
+        <v>0.02146892512912323</v>
       </c>
       <c r="Z5">
-        <v>0.2216257048048129</v>
+        <v>0.3122131389737023</v>
       </c>
       <c r="AA5">
-        <v>0.1155165455708277</v>
+        <v>0.05434801056637129</v>
       </c>
       <c r="AB5">
-        <v>0.07776756028288043</v>
+        <v>0.06156435843745595</v>
       </c>
       <c r="AC5">
-        <v>0.0377489852879473</v>
+        <v>-0.007216347871084661</v>
       </c>
       <c r="AD5">
-        <v>1577.1</v>
+        <v>18322.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1577.1</v>
+        <v>18322.9</v>
       </c>
       <c r="AG5">
-        <v>1179.5</v>
+        <v>18322.9</v>
       </c>
       <c r="AH5">
-        <v>0.2614035669296559</v>
+        <v>0.5695860585411952</v>
       </c>
       <c r="AI5">
-        <v>0.3240461073784134</v>
+        <v>0.615108046501791</v>
       </c>
       <c r="AJ5">
-        <v>0.2092944850592661</v>
+        <v>0.5695860585411952</v>
       </c>
       <c r="AK5">
-        <v>0.2639115745194997</v>
+        <v>0.615108046501791</v>
       </c>
       <c r="AL5">
-        <v>8.81</v>
+        <v>15.6</v>
       </c>
       <c r="AM5">
-        <v>8.81</v>
+        <v>15.6</v>
+      </c>
+      <c r="AN5">
+        <v>12.3636302294197</v>
       </c>
       <c r="AO5">
-        <v>57.25312145289443</v>
+        <v>92.1025641025641</v>
+      </c>
+      <c r="AP5">
+        <v>12.3636302294197</v>
       </c>
       <c r="AQ5">
-        <v>57.25312145289443</v>
+        <v>92.1025641025641</v>
       </c>
     </row>
     <row r="6">
@@ -1112,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IDI (ENXTPA:IDIP)</t>
+          <t>Audacia SA (ENXTPA:ALAUD)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1120,122 +1108,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.0663</v>
-      </c>
-      <c r="E6">
-        <v>-0.0688</v>
-      </c>
       <c r="G6">
-        <v>1.673492605233219</v>
+        <v>0.05727459016393444</v>
       </c>
       <c r="H6">
-        <v>1.673492605233219</v>
+        <v>0.05727459016393444</v>
       </c>
       <c r="I6">
-        <v>0.8077360637087599</v>
+        <v>0.06045081967213115</v>
       </c>
       <c r="J6">
-        <v>0.8077360637087599</v>
+        <v>0.04876515936376379</v>
       </c>
       <c r="K6">
-        <v>75.5</v>
+        <v>0.403</v>
       </c>
       <c r="L6">
-        <v>0.8589306029579067</v>
+        <v>0.04129098360655738</v>
       </c>
       <c r="M6">
-        <v>28.4</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.07713199348180337</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.376158940397351</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>28.4</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.07713199348180337</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.376158940397351</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>17.2</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>0.04671374253123303</v>
+        <v>0.0796812749003984</v>
       </c>
       <c r="W6">
-        <v>0.1102833771545428</v>
+        <v>0.03053030303030303</v>
       </c>
       <c r="X6">
-        <v>0.0811139926018983</v>
+        <v>0.0666643177056859</v>
       </c>
       <c r="Y6">
-        <v>0.02916938455264449</v>
+        <v>-0.03613401467538287</v>
       </c>
       <c r="Z6">
-        <v>0.1172156287505001</v>
+        <v>1.149587750294464</v>
       </c>
       <c r="AA6">
-        <v>0.09467929057207627</v>
+        <v>0.05605982984574022</v>
       </c>
       <c r="AB6">
-        <v>0.07632056557577317</v>
+        <v>0.06575166718052612</v>
       </c>
       <c r="AC6">
-        <v>0.0183587249963031</v>
+        <v>-0.009691837334785902</v>
       </c>
       <c r="AD6">
-        <v>48.6</v>
+        <v>0.82</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>48.6</v>
+        <v>0.82</v>
       </c>
       <c r="AG6">
-        <v>31.4</v>
+        <v>-1.18</v>
       </c>
       <c r="AH6">
-        <v>0.1166026871401152</v>
+        <v>0.0316358024691358</v>
       </c>
       <c r="AI6">
-        <v>0.0694980694980695</v>
+        <v>0.05317769130998703</v>
       </c>
       <c r="AJ6">
-        <v>0.07857857857857858</v>
+        <v>-0.04933110367892977</v>
       </c>
       <c r="AK6">
-        <v>0.04603430582026096</v>
+        <v>-0.08792846497764532</v>
       </c>
       <c r="AL6">
-        <v>0.973</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AM6">
-        <v>0.973</v>
+        <v>-0.016</v>
       </c>
       <c r="AN6">
-        <v>0.6797202797202797</v>
+        <v>1.401709401709402</v>
       </c>
       <c r="AO6">
-        <v>72.97019527235355</v>
+        <v>65.55555555555556</v>
       </c>
       <c r="AP6">
-        <v>0.4391608391608392</v>
+        <v>-2.017094017094017</v>
       </c>
       <c r="AQ6">
-        <v>72.97019527235355</v>
+        <v>-36.875</v>
       </c>
     </row>
     <row r="7">
@@ -1246,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Union Financière de France Banque SA (ENXTPA:UFF)</t>
+          <t>Compagnie Lebon (ENXTPA:ALBON)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1255,121 +1234,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0226</v>
+        <v>0.169</v>
       </c>
       <c r="E7">
-        <v>-0.263</v>
+        <v>-0.12</v>
       </c>
       <c r="G7">
-        <v>0.1154606563859233</v>
+        <v>0.1089176310415248</v>
       </c>
       <c r="H7">
-        <v>0.1154606563859233</v>
+        <v>0.1089176310415248</v>
       </c>
       <c r="I7">
-        <v>0.05140371688414393</v>
+        <v>0.07147719537100068</v>
       </c>
       <c r="J7">
-        <v>0.03334295149241769</v>
+        <v>0.04993336465354414</v>
       </c>
       <c r="K7">
-        <v>7.16</v>
+        <v>10.9</v>
       </c>
       <c r="L7">
-        <v>0.02831158560695927</v>
+        <v>0.0742001361470388</v>
       </c>
       <c r="M7">
-        <v>62.7</v>
+        <v>3.023</v>
       </c>
       <c r="N7">
-        <v>0.1714520098441346</v>
+        <v>0.02498347107438017</v>
       </c>
       <c r="O7">
-        <v>8.756983240223464</v>
+        <v>0.2773394495412844</v>
       </c>
       <c r="P7">
-        <v>62.7</v>
+        <v>2.99</v>
       </c>
       <c r="Q7">
-        <v>0.1714520098441346</v>
+        <v>0.02471074380165289</v>
       </c>
       <c r="R7">
-        <v>8.756983240223464</v>
+        <v>0.2743119266055046</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>0.03299999999999992</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.01091630830301023</v>
       </c>
       <c r="U7">
-        <v>120.4</v>
+        <v>60.3</v>
       </c>
       <c r="V7">
-        <v>0.3292316106097894</v>
+        <v>0.4983471074380165</v>
       </c>
       <c r="W7">
-        <v>0.03468992248062015</v>
+        <v>0.05838243170862346</v>
       </c>
       <c r="X7">
-        <v>0.07820261941564596</v>
+        <v>0.09384768008307021</v>
       </c>
       <c r="Y7">
-        <v>-0.04351269693502581</v>
+        <v>-0.03546524837444674</v>
       </c>
       <c r="Z7">
-        <v>2.01033386327504</v>
+        <v>0.6864485981308411</v>
       </c>
       <c r="AA7">
-        <v>0.06703046448674431</v>
+        <v>0.03427668816638146</v>
       </c>
       <c r="AB7">
-        <v>0.07722245859426692</v>
+        <v>0.0615049470999281</v>
       </c>
       <c r="AC7">
-        <v>-0.01019199410752261</v>
+        <v>-0.02722825893354664</v>
       </c>
       <c r="AD7">
-        <v>11.4</v>
+        <v>165.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>11.4</v>
+        <v>165.2</v>
       </c>
       <c r="AG7">
-        <v>-109</v>
+        <v>104.9</v>
       </c>
       <c r="AH7">
-        <v>0.03023070803500398</v>
+        <v>0.5772187281621244</v>
       </c>
       <c r="AI7">
-        <v>0.0782967032967033</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="AJ7">
-        <v>-0.4246201791975068</v>
+        <v>0.4643647631695441</v>
       </c>
       <c r="AK7">
-        <v>-4.325396825396827</v>
+        <v>0.3571671773918965</v>
       </c>
       <c r="AL7">
-        <v>0.652</v>
+        <v>4.5</v>
       </c>
       <c r="AM7">
-        <v>0.652</v>
+        <v>4.139</v>
       </c>
       <c r="AN7">
-        <v>0.5728643216080402</v>
+        <v>10.325</v>
       </c>
       <c r="AO7">
-        <v>19.93865030674846</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="AP7">
-        <v>-5.477386934673367</v>
+        <v>6.556249999999999</v>
       </c>
       <c r="AQ7">
-        <v>19.93865030674846</v>
+        <v>2.536844648465813</v>
       </c>
     </row>
     <row r="8">
@@ -1380,7 +1359,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amundi S.A. (ENXTPA:AMUN)</t>
+          <t>Tikehau Capital (ENXTPA:TKO)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1389,121 +1368,118 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.156</v>
+        <v>0.075</v>
       </c>
       <c r="E8">
-        <v>0.134</v>
+        <v>-0.0482</v>
       </c>
       <c r="F8">
-        <v>-0.00252</v>
+        <v>0.108</v>
       </c>
       <c r="G8">
-        <v>0.3296965918536991</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>0.3296965918536991</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.2526842615683015</v>
+        <v>0.3891741548994437</v>
       </c>
       <c r="J8">
-        <v>0.2083465343251663</v>
+        <v>0.3164407631985743</v>
       </c>
       <c r="K8">
-        <v>1070.3</v>
+        <v>125.4</v>
       </c>
       <c r="L8">
-        <v>0.1853525907453588</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>57.2</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.01463102698554803</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.456140350877193</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>57.2</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.01463102698554803</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.456140350877193</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>0</v>
+        <v>351.6</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>0.08993477426780919</v>
       </c>
       <c r="W8">
-        <v>0.09296124515781611</v>
+        <v>0.03820840950639854</v>
       </c>
       <c r="X8">
-        <v>0.1024759555439966</v>
+        <v>0.07450739389029493</v>
       </c>
       <c r="Y8">
-        <v>-0.009514710386180514</v>
+        <v>-0.03629898438389639</v>
       </c>
       <c r="Z8">
-        <v>0.2159348426036034</v>
+        <v>0.1166516921233902</v>
       </c>
       <c r="AA8">
-        <v>0.04498927609651102</v>
+        <v>0.03691335048393073</v>
       </c>
       <c r="AB8">
-        <v>0.07338057560595324</v>
+        <v>0.06587661519413805</v>
       </c>
       <c r="AC8">
-        <v>-0.02839129950944221</v>
+        <v>-0.02896326471020733</v>
       </c>
       <c r="AD8">
-        <v>10053.6</v>
+        <v>1630.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>10053.6</v>
+        <v>1630.9</v>
       </c>
       <c r="AG8">
-        <v>10053.6</v>
+        <v>1279.3</v>
       </c>
       <c r="AH8">
-        <v>0.4657420018345054</v>
+        <v>0.2943650277958271</v>
       </c>
       <c r="AI8">
-        <v>0.493702028609732</v>
+        <v>0.3256654485912259</v>
       </c>
       <c r="AJ8">
-        <v>0.4657420018345054</v>
+        <v>0.2465502621029911</v>
       </c>
       <c r="AK8">
-        <v>0.493702028609732</v>
+        <v>0.2747460429955115</v>
       </c>
       <c r="AL8">
-        <v>78.5</v>
+        <v>38.2</v>
       </c>
       <c r="AM8">
-        <v>78.5</v>
-      </c>
-      <c r="AN8">
-        <v>6.727966271832965</v>
+        <v>38.2</v>
       </c>
       <c r="AO8">
-        <v>18.58726114649681</v>
-      </c>
-      <c r="AP8">
-        <v>6.727966271832965</v>
+        <v>4.761780104712042</v>
       </c>
       <c r="AQ8">
-        <v>18.58726114649681</v>
+        <v>4.761780104712042</v>
       </c>
     </row>
     <row r="9">
@@ -1514,7 +1490,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Societe de Tayninh SA (ENXTPA:TAYN)</t>
+          <t>Altamir SCA (ENXTPA:LTA)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1522,89 +1498,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.0264</v>
+      </c>
+      <c r="E9">
+        <v>-0.00385</v>
+      </c>
+      <c r="G9">
+        <v>-0.1961805555555556</v>
+      </c>
+      <c r="H9">
+        <v>-0.1961805555555556</v>
+      </c>
+      <c r="I9">
+        <v>0.4756944444444444</v>
+      </c>
+      <c r="J9">
+        <v>0.4756944444444444</v>
+      </c>
       <c r="K9">
-        <v>-0.099</v>
+        <v>24.2</v>
+      </c>
+      <c r="L9">
+        <v>0.4201388888888888</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>43.07</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.04486925721429316</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.779752066115702</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>43.07</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.04486925721429316</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.779752066115702</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>0.001</v>
+        <v>111.7</v>
       </c>
       <c r="V9">
-        <v>8.47457627118644e-05</v>
+        <v>0.1163662881550162</v>
       </c>
       <c r="W9">
-        <v>-0.004876847290640394</v>
+        <v>0.0177915012498162</v>
       </c>
       <c r="X9">
-        <v>0.07730243933280354</v>
+        <v>0.07105980382206908</v>
       </c>
       <c r="Y9">
-        <v>-0.08217928662344393</v>
+        <v>-0.05326830257225288</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>0.04816077672630464</v>
       </c>
       <c r="AA9">
-        <v>-0.005369458128078817</v>
+        <v>0.02290981392883241</v>
       </c>
       <c r="AB9">
-        <v>0.07730243933280354</v>
+        <v>0.064450375790482</v>
       </c>
       <c r="AC9">
-        <v>-0.08267189746088235</v>
+        <v>-0.04154056186164959</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>238.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>238.2</v>
       </c>
       <c r="AG9">
-        <v>-0.001</v>
+        <v>126.5</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.1988147900843001</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.1452261919278137</v>
       </c>
       <c r="AJ9">
-        <v>-8.475294516484447e-05</v>
+        <v>0.116439617083947</v>
       </c>
       <c r="AK9">
-        <v>-5.618293162537222e-05</v>
+        <v>0.0827608766764802</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="AM9">
-        <v>-0.008999999999999999</v>
+        <v>-0.0699999999999994</v>
+      </c>
+      <c r="AN9">
+        <v>8.357894736842105</v>
+      </c>
+      <c r="AO9">
+        <v>5.792811839323466</v>
+      </c>
+      <c r="AP9">
+        <v>4.438596491228069</v>
       </c>
       <c r="AQ9">
-        <v>12.11111111111111</v>
+        <v>-391.4285714285748</v>
       </c>
     </row>
     <row r="10">
@@ -1615,7 +1624,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Compagnie Lebon (ENXTPA:ALBON)</t>
+          <t>Compagnie des Tramways de Rouen (ENXTPA:MLTRA)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1623,122 +1632,71 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D10">
-        <v>0.0271</v>
-      </c>
-      <c r="E10">
-        <v>-0.147</v>
-      </c>
-      <c r="G10">
-        <v>-0.04625</v>
-      </c>
-      <c r="H10">
-        <v>-0.04625</v>
-      </c>
-      <c r="I10">
-        <v>-0.02583543169821402</v>
-      </c>
-      <c r="J10">
-        <v>-0.02583543169821402</v>
-      </c>
       <c r="K10">
-        <v>8.99</v>
-      </c>
-      <c r="L10">
-        <v>0.07491666666666667</v>
+        <v>-0.017</v>
       </c>
       <c r="M10">
-        <v>2.901</v>
+        <v>0.3609</v>
       </c>
       <c r="N10">
-        <v>0.02797492767598843</v>
+        <v>0.006265624999999999</v>
       </c>
       <c r="O10">
-        <v>0.3226918798665184</v>
+        <v>-21.22941176470588</v>
       </c>
       <c r="P10">
-        <v>2.87</v>
+        <v>0.3609</v>
       </c>
       <c r="Q10">
-        <v>0.02767598842815815</v>
+        <v>0.006265624999999999</v>
       </c>
       <c r="R10">
-        <v>0.3192436040044494</v>
+        <v>-21.22941176470588</v>
       </c>
       <c r="S10">
-        <v>0.03100000000000014</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.01068597035505003</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>53.4</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>0.5149469623915139</v>
-      </c>
-      <c r="W10">
-        <v>0.04716684155299056</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>0.1246335007264621</v>
-      </c>
-      <c r="Y10">
-        <v>-0.07746665917347156</v>
-      </c>
-      <c r="Z10">
-        <v>0.5410980689330799</v>
-      </c>
-      <c r="AA10">
-        <v>-0.01397950220195609</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AB10">
-        <v>0.07207253921301257</v>
-      </c>
-      <c r="AC10">
-        <v>-0.08605204141496865</v>
+        <v>0.06599791461842178</v>
       </c>
       <c r="AD10">
-        <v>167.5</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>2.471259018928411</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>169.9712590189284</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>116.5712590189284</v>
+        <v>0</v>
       </c>
       <c r="AH10">
-        <v>0.6210782222007916</v>
-      </c>
-      <c r="AI10">
-        <v>0.4870637756724517</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0.5292168371767066</v>
-      </c>
-      <c r="AK10">
-        <v>0.3943930793740104</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>4.322</v>
-      </c>
-      <c r="AN10">
-        <v>552.8052805280528</v>
-      </c>
-      <c r="AO10">
-        <v>-0.6139954853273139</v>
-      </c>
-      <c r="AP10">
-        <v>384.7236271251763</v>
+        <v>-0.019</v>
       </c>
       <c r="AQ10">
-        <v>-0.6293382693197594</v>
+        <v>1.894736842105263</v>
       </c>
     </row>
     <row r="11">
@@ -1758,299 +1716,106 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0382</v>
-      </c>
-      <c r="E11">
-        <v>1.026</v>
+        <v>0.00601</v>
       </c>
       <c r="G11">
-        <v>-2.623529411764706</v>
+        <v>-2.058252427184466</v>
       </c>
       <c r="H11">
-        <v>-2.623529411764706</v>
+        <v>-2.058252427184466</v>
       </c>
       <c r="I11">
-        <v>-2.585663158011433</v>
+        <v>-2.528478445729528</v>
       </c>
       <c r="J11">
-        <v>-2.467486800617784</v>
+        <v>-2.528478445729528</v>
       </c>
       <c r="K11">
-        <v>55.5</v>
+        <v>-11.7</v>
       </c>
       <c r="L11">
-        <v>65.29411764705883</v>
+        <v>-11.35922330097087</v>
       </c>
       <c r="M11">
-        <v>0.8514999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.01166438356164383</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.01534234234234234</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>0.6435</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.008815068493150684</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.01159459459459459</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>0.208</v>
-      </c>
-      <c r="T11">
-        <v>0.2442748091603053</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>0.863</v>
+        <v>1.52</v>
       </c>
       <c r="V11">
-        <v>0.01182191780821918</v>
+        <v>0.03636363636363637</v>
       </c>
       <c r="W11">
-        <v>2.875647668393782</v>
+        <v>5.270270270270269</v>
       </c>
       <c r="X11">
-        <v>0.07799827931755962</v>
+        <v>0.07200357723661688</v>
       </c>
       <c r="Y11">
-        <v>2.797649389076223</v>
-      </c>
-      <c r="Z11">
-        <v>0.05148685427280263</v>
-      </c>
-      <c r="AA11">
-        <v>-0.1270431333234718</v>
+        <v>5.198266693033652</v>
       </c>
       <c r="AB11">
-        <v>0.07724018695528731</v>
-      </c>
-      <c r="AC11">
-        <v>-0.2042833202787591</v>
+        <v>0.06422746957281771</v>
       </c>
       <c r="AD11">
-        <v>1.69</v>
+        <v>12.3</v>
       </c>
       <c r="AE11">
-        <v>0.06906842154859023</v>
+        <v>0.006663995507069127</v>
       </c>
       <c r="AF11">
-        <v>1.75906842154859</v>
+        <v>12.30666399550707</v>
       </c>
       <c r="AG11">
-        <v>0.8960684215485901</v>
+        <v>10.78666399550707</v>
       </c>
       <c r="AH11">
-        <v>0.02352983335251881</v>
+        <v>0.2274519086323451</v>
       </c>
       <c r="AI11">
-        <v>-3.816333060664936</v>
+        <v>-7.267703493490825</v>
       </c>
       <c r="AJ11">
-        <v>0.01212606354693818</v>
+        <v>0.20512166347781</v>
       </c>
       <c r="AK11">
-        <v>-0.6768238148656539</v>
+        <v>-3.356842851300022</v>
       </c>
       <c r="AL11">
-        <v>0.051</v>
+        <v>0.213</v>
       </c>
       <c r="AM11">
-        <v>-4.548999999999999</v>
+        <v>-4.617</v>
       </c>
       <c r="AN11">
-        <v>-0.8693415637860082</v>
+        <v>-5.272181740248608</v>
       </c>
       <c r="AO11">
-        <v>-43.92156862745099</v>
+        <v>-12.25352112676056</v>
       </c>
       <c r="AP11">
-        <v>-0.4609405460640896</v>
+        <v>-4.623516500431664</v>
       </c>
       <c r="AQ11">
-        <v>0.4924159155858431</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Société des Chemins de Fer et Tramways du Var et du Gard (ENXTPA:MLCVG)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="E12">
-        <v>-0.124</v>
-      </c>
-      <c r="K12">
-        <v>1.24</v>
-      </c>
-      <c r="M12">
-        <v>0.7875</v>
-      </c>
-      <c r="N12">
-        <v>0.001865671641791045</v>
-      </c>
-      <c r="O12">
-        <v>0.6350806451612903</v>
-      </c>
-      <c r="P12">
-        <v>0.7875</v>
-      </c>
-      <c r="Q12">
-        <v>0.001865671641791045</v>
-      </c>
-      <c r="R12">
-        <v>0.6350806451612903</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0.07730243933280354</v>
-      </c>
-      <c r="AB12">
-        <v>0.07730243933280354</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-1.36</v>
-      </c>
-      <c r="AQ12">
-        <v>0.07720588235294117</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Financière Marjos SA (ENXTPA:FINM)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K13">
-        <v>-0.034</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0.001</v>
-      </c>
-      <c r="V13">
-        <v>0.0003610108303249097</v>
-      </c>
-      <c r="W13">
-        <v>0.03732162458836444</v>
-      </c>
-      <c r="X13">
-        <v>0.07956463139107567</v>
-      </c>
-      <c r="Y13">
-        <v>-0.04224300680271123</v>
-      </c>
-      <c r="AB13">
-        <v>0.0771102356953756</v>
-      </c>
-      <c r="AD13">
-        <v>0.217</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0.217</v>
-      </c>
-      <c r="AG13">
-        <v>0.216</v>
-      </c>
-      <c r="AH13">
-        <v>0.07264814194844325</v>
-      </c>
-      <c r="AI13">
-        <v>-0.35</v>
-      </c>
-      <c r="AJ13">
-        <v>0.07233757535164098</v>
-      </c>
-      <c r="AK13">
-        <v>-0.3478260869565217</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>-0.004</v>
-      </c>
-      <c r="AQ13">
-        <v>28.5</v>
+        <v>0.5653021442495126</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/france/france_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,118 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.13</v>
+        <v>0.08925</v>
       </c>
       <c r="E2">
-        <v>0.179</v>
+        <v>0.0711</v>
       </c>
       <c r="F2">
-        <v>0.354</v>
+        <v>0.083</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2455003012350638</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.2455003012350638</v>
       </c>
       <c r="I2">
-        <v>0.4468485418626529</v>
+        <v>0.287155211366603</v>
       </c>
       <c r="J2">
-        <v>0.4074827552696137</v>
+        <v>0.2586231498261554</v>
       </c>
       <c r="K2">
-        <v>173.8</v>
+        <v>1762.285</v>
       </c>
       <c r="L2">
-        <v>0.3269990592662277</v>
+        <v>0.2211925143086655</v>
       </c>
       <c r="M2">
-        <v>140.6</v>
+        <v>328.326</v>
       </c>
       <c r="N2">
-        <v>0.03850999726102437</v>
+        <v>0.01619283882422569</v>
       </c>
       <c r="O2">
-        <v>0.8089758342922899</v>
+        <v>0.1863069821283164</v>
       </c>
       <c r="P2">
-        <v>140.6</v>
+        <v>323.46</v>
       </c>
       <c r="Q2">
-        <v>0.03850999726102437</v>
+        <v>0.01595285066087986</v>
       </c>
       <c r="R2">
-        <v>0.8089758342922899</v>
+        <v>0.1835457942387298</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>4.866000000000009</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.01482063558779996</v>
       </c>
       <c r="U2">
-        <v>233.7</v>
+        <v>719.1</v>
       </c>
       <c r="V2">
-        <v>0.06400986031224322</v>
+        <v>0.03546557506411521</v>
       </c>
       <c r="W2">
-        <v>0.05156810966382815</v>
+        <v>0.04425440940673436</v>
       </c>
       <c r="X2">
-        <v>0.08219144900556109</v>
+        <v>0.0772987249513587</v>
       </c>
       <c r="Y2">
-        <v>-0.03062333934173295</v>
+        <v>-0.03304431554462434</v>
       </c>
       <c r="Z2">
-        <v>0.1272200679783618</v>
+        <v>0.222591133792157</v>
       </c>
       <c r="AA2">
-        <v>0.05183998382541043</v>
+        <v>0.04653883606261327</v>
       </c>
       <c r="AB2">
-        <v>0.07099044605054713</v>
+        <v>0.07097923892900693</v>
       </c>
       <c r="AC2">
-        <v>-0.01915046222513671</v>
+        <v>-0.01981158370722803</v>
       </c>
       <c r="AD2">
-        <v>1885.6</v>
+        <v>25072.77</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1885.6</v>
+        <v>25072.77</v>
       </c>
       <c r="AG2">
-        <v>1651.9</v>
+        <v>24353.67</v>
       </c>
       <c r="AH2">
-        <v>0.3405700249250442</v>
+        <v>0.5528875424846142</v>
       </c>
       <c r="AI2">
-        <v>0.3597512115083756</v>
+        <v>0.5804060634274157</v>
       </c>
       <c r="AJ2">
-        <v>0.3115087970732995</v>
+        <v>0.5456833985104529</v>
       </c>
       <c r="AK2">
-        <v>0.3298719971244284</v>
+        <v>0.5733031195937246</v>
       </c>
       <c r="AL2">
-        <v>65.7</v>
+        <v>195.07</v>
       </c>
       <c r="AM2">
-        <v>65.7</v>
+        <v>183.372</v>
+      </c>
+      <c r="AN2">
+        <v>11.93757248881601</v>
       </c>
       <c r="AO2">
-        <v>3.614916286149163</v>
+        <v>11.72821551238017</v>
+      </c>
+      <c r="AP2">
+        <v>11.59519674107423</v>
       </c>
       <c r="AQ2">
-        <v>3.614916286149163</v>
+        <v>12.47640315860655</v>
       </c>
     </row>
     <row r="3">
@@ -710,127 +716,886 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Antin Infrastructure Partners SAS (ENXTPA:ANTIN)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>0.083</v>
+      </c>
+      <c r="G3">
+        <v>0.5744</v>
+      </c>
+      <c r="H3">
+        <v>0.5744</v>
+      </c>
+      <c r="I3">
+        <v>0.54656</v>
+      </c>
+      <c r="J3">
+        <v>0.4224191163658992</v>
+      </c>
+      <c r="K3">
+        <v>124.2</v>
+      </c>
+      <c r="L3">
+        <v>0.39744</v>
+      </c>
+      <c r="M3">
+        <v>140.49</v>
+      </c>
+      <c r="N3">
+        <v>0.06874633000587199</v>
+      </c>
+      <c r="O3">
+        <v>1.131159420289855</v>
+      </c>
+      <c r="P3">
+        <v>136</v>
+      </c>
+      <c r="Q3">
+        <v>0.06654922685457038</v>
+      </c>
+      <c r="R3">
+        <v>1.095008051529791</v>
+      </c>
+      <c r="S3">
+        <v>4.490000000000009</v>
+      </c>
+      <c r="T3">
+        <v>0.03195957007616207</v>
+      </c>
+      <c r="U3">
+        <v>420.1</v>
+      </c>
+      <c r="V3">
+        <v>0.2055686044235663</v>
+      </c>
+      <c r="W3">
+        <v>0.2354948805460751</v>
+      </c>
+      <c r="X3">
+        <v>0.0725845227888206</v>
+      </c>
+      <c r="Y3">
+        <v>0.1629103577572545</v>
+      </c>
+      <c r="Z3">
+        <v>2.460629921259843</v>
+      </c>
+      <c r="AA3">
+        <v>1.039417117042075</v>
+      </c>
+      <c r="AB3">
+        <v>0.0718389771528023</v>
+      </c>
+      <c r="AC3">
+        <v>0.9675781398892724</v>
+      </c>
+      <c r="AD3">
+        <v>58.8</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>58.8</v>
+      </c>
+      <c r="AG3">
+        <v>-361.3</v>
+      </c>
+      <c r="AH3">
+        <v>0.02796803652968036</v>
+      </c>
+      <c r="AI3">
+        <v>0.1011351909184726</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.2147654996136242</v>
+      </c>
+      <c r="AK3">
+        <v>-2.239925604463732</v>
+      </c>
+      <c r="AL3">
+        <v>2.34</v>
+      </c>
+      <c r="AM3">
+        <v>-6.81</v>
+      </c>
+      <c r="AN3">
+        <v>0.3430571761960327</v>
+      </c>
+      <c r="AO3">
+        <v>72.991452991453</v>
+      </c>
+      <c r="AP3">
+        <v>-2.107934655775963</v>
+      </c>
+      <c r="AQ3">
+        <v>-25.08076358296623</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Compagnie Lebon (ENXTPA:ALBON)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.201</v>
+      </c>
+      <c r="E4">
+        <v>0.0708</v>
+      </c>
+      <c r="G4">
+        <v>0.1108829568788501</v>
+      </c>
+      <c r="H4">
+        <v>0.1108829568788501</v>
+      </c>
+      <c r="I4">
+        <v>0.09445585215605751</v>
+      </c>
+      <c r="J4">
+        <v>0.08035342095338083</v>
+      </c>
+      <c r="K4">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="L4">
+        <v>0.05667351129363449</v>
+      </c>
+      <c r="M4">
+        <v>4.896</v>
+      </c>
+      <c r="N4">
+        <v>0.0443076923076923</v>
+      </c>
+      <c r="O4">
+        <v>0.591304347826087</v>
+      </c>
+      <c r="P4">
+        <v>4.52</v>
+      </c>
+      <c r="Q4">
+        <v>0.04090497737556561</v>
+      </c>
+      <c r="R4">
+        <v>0.5458937198067633</v>
+      </c>
+      <c r="S4">
+        <v>0.3760000000000003</v>
+      </c>
+      <c r="T4">
+        <v>0.07679738562091511</v>
+      </c>
+      <c r="U4">
+        <v>26.6</v>
+      </c>
+      <c r="V4">
+        <v>0.2407239819004525</v>
+      </c>
+      <c r="W4">
+        <v>0.04425440940673436</v>
+      </c>
+      <c r="X4">
+        <v>0.0958825272287053</v>
+      </c>
+      <c r="Y4">
+        <v>-0.05162811782197094</v>
+      </c>
+      <c r="Z4">
+        <v>0.7225519287833829</v>
+      </c>
+      <c r="AA4">
+        <v>0.05805951929420841</v>
+      </c>
+      <c r="AB4">
+        <v>0.06705592591825962</v>
+      </c>
+      <c r="AC4">
+        <v>-0.008996406624051212</v>
+      </c>
+      <c r="AD4">
+        <v>134.1</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>134.1</v>
+      </c>
+      <c r="AG4">
+        <v>107.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.5482420278004906</v>
+      </c>
+      <c r="AI4">
+        <v>0.4127423822714681</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4931192660550459</v>
+      </c>
+      <c r="AK4">
+        <v>0.360375460945357</v>
+      </c>
+      <c r="AL4">
+        <v>6.84</v>
+      </c>
+      <c r="AM4">
+        <v>5.18</v>
+      </c>
+      <c r="AN4">
+        <v>8.596153846153847</v>
+      </c>
+      <c r="AO4">
+        <v>2.017543859649123</v>
+      </c>
+      <c r="AP4">
+        <v>6.891025641025641</v>
+      </c>
+      <c r="AQ4">
+        <v>2.664092664092665</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>Tikehau Capital (ENXTPA:TKO)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D5">
         <v>0.13</v>
       </c>
-      <c r="E3">
+      <c r="E5">
         <v>0.179</v>
       </c>
-      <c r="F3">
+      <c r="F5">
         <v>0.354</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>0.4468485418626529</v>
       </c>
-      <c r="J3">
+      <c r="J5">
         <v>0.4074827552696137</v>
       </c>
-      <c r="K3">
+      <c r="K5">
         <v>173.8</v>
       </c>
-      <c r="L3">
+      <c r="L5">
         <v>0.3269990592662277</v>
       </c>
-      <c r="M3">
+      <c r="M5">
         <v>140.6</v>
       </c>
-      <c r="N3">
+      <c r="N5">
         <v>0.03850999726102437</v>
       </c>
-      <c r="O3">
+      <c r="O5">
         <v>0.8089758342922899</v>
       </c>
-      <c r="P3">
+      <c r="P5">
         <v>140.6</v>
       </c>
-      <c r="Q3">
+      <c r="Q5">
         <v>0.03850999726102437</v>
       </c>
-      <c r="R3">
+      <c r="R5">
         <v>0.8089758342922899</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <v>233.7</v>
       </c>
-      <c r="V3">
+      <c r="V5">
         <v>0.06400986031224322</v>
       </c>
-      <c r="W3">
+      <c r="W5">
         <v>0.05156810966382815</v>
       </c>
-      <c r="X3">
-        <v>0.08219144900556109</v>
-      </c>
-      <c r="Y3">
-        <v>-0.03062333934173295</v>
-      </c>
-      <c r="Z3">
+      <c r="X5">
+        <v>0.08217445384009425</v>
+      </c>
+      <c r="Y5">
+        <v>-0.03060634417626611</v>
+      </c>
+      <c r="Z5">
         <v>0.1272200679783618</v>
       </c>
-      <c r="AA3">
+      <c r="AA5">
         <v>0.05183998382541043</v>
       </c>
-      <c r="AB3">
-        <v>0.07099044605054713</v>
-      </c>
-      <c r="AC3">
-        <v>-0.01915046222513671</v>
-      </c>
-      <c r="AD3">
+      <c r="AB5">
+        <v>0.07097923892900693</v>
+      </c>
+      <c r="AC5">
+        <v>-0.0191392551035965</v>
+      </c>
+      <c r="AD5">
         <v>1885.6</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
         <v>1885.6</v>
       </c>
-      <c r="AG3">
+      <c r="AG5">
         <v>1651.9</v>
       </c>
-      <c r="AH3">
+      <c r="AH5">
         <v>0.3405700249250442</v>
       </c>
-      <c r="AI3">
+      <c r="AI5">
         <v>0.3597512115083756</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ5">
         <v>0.3115087970732995</v>
       </c>
-      <c r="AK3">
+      <c r="AK5">
         <v>0.3298719971244284</v>
       </c>
-      <c r="AL3">
+      <c r="AL5">
         <v>65.7</v>
       </c>
-      <c r="AM3">
+      <c r="AM5">
         <v>65.7</v>
       </c>
-      <c r="AO3">
+      <c r="AO5">
         <v>3.614916286149163</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ5">
         <v>3.614916286149163</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Amundi S.A. (ENXTPA:AMUN)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.04849999999999999</v>
+      </c>
+      <c r="E6">
+        <v>0.07139999999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.0736</v>
+      </c>
+      <c r="G6">
+        <v>0.250094435565887</v>
+      </c>
+      <c r="H6">
+        <v>0.250094435565887</v>
+      </c>
+      <c r="I6">
+        <v>0.2613831178265291</v>
+      </c>
+      <c r="J6">
+        <v>0.201004093033993</v>
+      </c>
+      <c r="K6">
+        <v>1399.6</v>
+      </c>
+      <c r="L6">
+        <v>0.2033415661775388</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.122715954126188</v>
+      </c>
+      <c r="X6">
+        <v>0.1049575883345901</v>
+      </c>
+      <c r="Y6">
+        <v>0.01775836579159798</v>
+      </c>
+      <c r="Z6">
+        <v>0.2315317830604714</v>
+      </c>
+      <c r="AA6">
+        <v>0.04653883606261327</v>
+      </c>
+      <c r="AB6">
+        <v>0.0663504197698413</v>
+      </c>
+      <c r="AC6">
+        <v>-0.01981158370722803</v>
+      </c>
+      <c r="AD6">
+        <v>22764</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>22764</v>
+      </c>
+      <c r="AG6">
+        <v>22764</v>
+      </c>
+      <c r="AH6">
+        <v>0.6261793815227018</v>
+      </c>
+      <c r="AI6">
+        <v>0.6430871800666704</v>
+      </c>
+      <c r="AJ6">
+        <v>0.6261793815227018</v>
+      </c>
+      <c r="AK6">
+        <v>0.6430871800666704</v>
+      </c>
+      <c r="AL6">
+        <v>116.4</v>
+      </c>
+      <c r="AM6">
+        <v>116.4</v>
+      </c>
+      <c r="AN6">
+        <v>12.34825061025224</v>
+      </c>
+      <c r="AO6">
+        <v>15.45618556701031</v>
+      </c>
+      <c r="AP6">
+        <v>12.34825061025224</v>
+      </c>
+      <c r="AQ6">
+        <v>15.45618556701031</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Altamir SCA (ENXTPA:LTA)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>-0.19</v>
+      </c>
+      <c r="E7">
+        <v>-0.19</v>
+      </c>
+      <c r="G7">
+        <v>0.4723247232472325</v>
+      </c>
+      <c r="H7">
+        <v>0.4723247232472325</v>
+      </c>
+      <c r="I7">
+        <v>0.8302583025830259</v>
+      </c>
+      <c r="J7">
+        <v>0.8302583025830259</v>
+      </c>
+      <c r="K7">
+        <v>55.9</v>
+      </c>
+      <c r="L7">
+        <v>0.6875768757687577</v>
+      </c>
+      <c r="M7">
+        <v>42.34</v>
+      </c>
+      <c r="N7">
+        <v>0.04960168697282099</v>
+      </c>
+      <c r="O7">
+        <v>0.7574239713774596</v>
+      </c>
+      <c r="P7">
+        <v>42.34</v>
+      </c>
+      <c r="Q7">
+        <v>0.04960168697282099</v>
+      </c>
+      <c r="R7">
+        <v>0.7574239713774596</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>36.8</v>
+      </c>
+      <c r="V7">
+        <v>0.04311152764761012</v>
+      </c>
+      <c r="W7">
+        <v>0.0398716119828816</v>
+      </c>
+      <c r="X7">
+        <v>0.0772987249513587</v>
+      </c>
+      <c r="Y7">
+        <v>-0.0374271129684771</v>
+      </c>
+      <c r="Z7">
+        <v>0.05318940137389597</v>
+      </c>
+      <c r="AA7">
+        <v>0.04416094210009813</v>
+      </c>
+      <c r="AB7">
+        <v>0.07010261915660269</v>
+      </c>
+      <c r="AC7">
+        <v>-0.02594167705650456</v>
+      </c>
+      <c r="AD7">
+        <v>229.2</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>229.2</v>
+      </c>
+      <c r="AG7">
+        <v>192.4</v>
+      </c>
+      <c r="AH7">
+        <v>0.2116734392316217</v>
+      </c>
+      <c r="AI7">
+        <v>0.1415951071847779</v>
+      </c>
+      <c r="AJ7">
+        <v>0.1839388145315487</v>
+      </c>
+      <c r="AK7">
+        <v>0.1216258929135849</v>
+      </c>
+      <c r="AL7">
+        <v>3.78</v>
+      </c>
+      <c r="AM7">
+        <v>3.78</v>
+      </c>
+      <c r="AN7">
+        <v>3.251063829787234</v>
+      </c>
+      <c r="AO7">
+        <v>17.85714285714286</v>
+      </c>
+      <c r="AP7">
+        <v>2.729078014184397</v>
+      </c>
+      <c r="AQ7">
+        <v>17.85714285714286</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Societe de Tayninh SA (ENXTPA:TAYN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K8">
+        <v>0.669</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.03558510638297872</v>
+      </c>
+      <c r="X8">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="Y8">
+        <v>-0.03643362752095085</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>-0.006542553191489361</v>
+      </c>
+      <c r="AB8">
+        <v>0.07201873390392957</v>
+      </c>
+      <c r="AC8">
+        <v>-0.07856128709541893</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-0.793</v>
+      </c>
+      <c r="AQ8">
+        <v>0.1551071878940731</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Audacia SA (ENXTPA:ALAUD)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0.03515625</v>
+      </c>
+      <c r="H9">
+        <v>0.03515625</v>
+      </c>
+      <c r="I9">
+        <v>-0.05890625</v>
+      </c>
+      <c r="J9">
+        <v>-0.05890625</v>
+      </c>
+      <c r="K9">
+        <v>-0.164</v>
+      </c>
+      <c r="L9">
+        <v>-0.0128125</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1.9</v>
+      </c>
+      <c r="V9">
+        <v>0.1180124223602484</v>
+      </c>
+      <c r="W9">
+        <v>-0.01154929577464789</v>
+      </c>
+      <c r="X9">
+        <v>0.0733255993671534</v>
+      </c>
+      <c r="Y9">
+        <v>-0.08487489514180128</v>
+      </c>
+      <c r="Z9">
+        <v>1.209829867674858</v>
+      </c>
+      <c r="AA9">
+        <v>-0.07126654064272211</v>
+      </c>
+      <c r="AB9">
+        <v>0.07145461762858785</v>
+      </c>
+      <c r="AC9">
+        <v>-0.14272115827131</v>
+      </c>
+      <c r="AD9">
+        <v>1.07</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>1.07</v>
+      </c>
+      <c r="AG9">
+        <v>-0.8299999999999998</v>
+      </c>
+      <c r="AH9">
+        <v>0.0623179965055329</v>
+      </c>
+      <c r="AI9">
+        <v>0.0710019907100199</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.05435494433529796</v>
+      </c>
+      <c r="AK9">
+        <v>-0.06302201974183749</v>
+      </c>
+      <c r="AL9">
+        <v>0.01</v>
+      </c>
+      <c r="AM9">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="AN9">
+        <v>-1.582840236686391</v>
+      </c>
+      <c r="AO9">
+        <v>-75.40000000000001</v>
+      </c>
+      <c r="AP9">
+        <v>1.227810650887574</v>
+      </c>
+      <c r="AQ9">
+        <v>8.870588235294116</v>
       </c>
     </row>
   </sheetData>
